--- a/grn_df.xlsx
+++ b/grn_df.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB7"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,612 +574,104 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7638551</v>
+        <v>7686779</v>
       </c>
       <c r="C2" t="n">
         <v>82</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24001844</t>
+          <t>24004829</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>45406.69809027778</v>
+        <v>45580.66552083333</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10061</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kobian Kenya Ltd</t>
+          <t>Jalaram Industrial Supplies Ltd</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nairobi - KES</t>
+          <t>Mombasa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>P.O. Box 46617</t>
+          <t>P.O. Box 97044</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Nairobi  00100 KE</t>
+          <t>Mombasa   KE</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1054</v>
+        <v>1025</v>
       </c>
       <c r="N2" t="n">
-        <v>1195</v>
+        <v>1028</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>32412212</t>
+          <t>424002297</t>
         </is>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45559.3634375</v>
+        <v>45583.42061342593</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>120667b 29-APR-24</t>
+          <t>126757 16-OCT-24</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>10197054</v>
+        <v>10205511</v>
       </c>
       <c r="U2" t="n">
-        <v>10393230</v>
+        <v>10402167</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>OTLCC0001054</t>
+          <t>OTMCT0003025</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>3241</v>
+        <v>5524</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Petroleum Ether AR</t>
+          <t>Silicon Tube - Black</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>LTR</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>32412212</t>
+          <t>424002297</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>ENG</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>7638551</v>
-      </c>
-      <c r="C3" t="n">
-        <v>82</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>24001844</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>45406.69809027778</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10061</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Kobian Kenya Ltd</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Nairobi - KES</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>P.O. Box 46617</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Nairobi  00100 KE</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>1054</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1195</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>32412212</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>45559.3634375</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>120667b 29-APR-24</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>10197054</v>
-      </c>
-      <c r="U3" t="n">
-        <v>10393232</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>OTLCI0007406</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>1130022</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Isooctane</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>LTR</t>
-        </is>
-      </c>
-      <c r="Z3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>32412212</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>7638551</v>
-      </c>
-      <c r="C4" t="n">
-        <v>82</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>24001844</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>45406.69809027778</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10061</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Kobian Kenya Ltd</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Nairobi - KES</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>P.O. Box 46617</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Nairobi  00100 KE</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>1054</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1195</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>32412212</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>45559.3634375</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>120667b 29-APR-24</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>10197054</v>
-      </c>
-      <c r="U4" t="n">
-        <v>10393231</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>OTLCA0003899</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
-        <v>164006</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Acetic Acid AR -(Monhydrous/Anhydrous)</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>LTR</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>32412212</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>ENG</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7638551</v>
-      </c>
-      <c r="C5" t="n">
-        <v>82</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>24001844</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>45406.69809027778</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>10061</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Kobian Kenya Ltd</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Nairobi - KES</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>P.O. Box 46617</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Nairobi  00100 KE</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>1054</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1195</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>12407080</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>45559.36087962963</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>120667 29-APR-24</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="n">
-        <v>10197053</v>
-      </c>
-      <c r="U5" t="n">
-        <v>10393228</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>OTLCH0009016</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>1425026</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Hydrochloric Acid Conc</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>LTR</t>
-        </is>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>12407080</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7638551</v>
-      </c>
-      <c r="C6" t="n">
-        <v>82</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>24001844</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>45406.69809027778</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>10061</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Kobian Kenya Ltd</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Nairobi - KES</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>P.O. Box 46617</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Nairobi  00100 KE</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1054</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1195</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>12407080</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>45559.36087962963</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>120667 29-APR-24</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>10197053</v>
-      </c>
-      <c r="U6" t="n">
-        <v>10393229</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>OTLCS0009032</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>1425042</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Sulphuric Acid Conc</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>LTR</t>
-        </is>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>12407080</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7638551</v>
-      </c>
-      <c r="C7" t="n">
-        <v>82</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>24001844</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>45406.69809027778</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>10061</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Kobian Kenya Ltd</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Nairobi - KES</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>P.O. Box 46617</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Nairobi  00100 KE</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1054</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1195</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>12407080</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>45559.36087962963</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>120667 29-APR-24</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="n">
-        <v>10197053</v>
-      </c>
-      <c r="U7" t="n">
-        <v>10393227</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>OTLCA0008998</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>1423024</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Acetone</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>LTR</t>
-        </is>
-      </c>
-      <c r="Z7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>12407080</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr"/>
+          <t>ENG_SPARE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
